--- a/data/cy2027/PlanMaterialsData.xlsx
+++ b/data/cy2027/PlanMaterialsData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/PlanMaterialAutomation/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://molinahealthcare-my.sharepoint.com/personal/naresh_jangid_molinahealthcare_com/Documents/Automation/molina_automation/PlanMaterialAutomation/data/cy2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_ACCBE32820397D6A206102BBF0179E13A12C8C3D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4399F0E7-7DF9-4B48-8611-590EC6DD375A}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_EBF33460A216A24A00A0126A4016A4F540A2DBEA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54D2F2B8-CFB5-421C-B8CC-C0712273C61F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
   <si>
     <t>Run</t>
   </si>
@@ -40,60 +40,72 @@
     <t>ExpectedUrl</t>
   </si>
   <si>
+    <t>TestId</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>Annual Notice of Change (ANOC)</t>
+  </si>
+  <si>
+    <t>2027 Annual Notice of Change – Molina Medicare Complete Care (HMO D-SNP)</t>
+  </si>
+  <si>
+    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/MI/2027-Materials/English/MI-H5926-1-0-AC-EN-27-S-508.pdf</t>
+  </si>
+  <si>
+    <t>TC003 MI Plan Materials — Annual Notice of Change (ANOC)</t>
+  </si>
+  <si>
+    <t>2027 Annual Notice of Change – Molina Dual MI Coordinated Health (HMO D-SNP) - Macomb, Wayne</t>
+  </si>
+  <si>
+    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/MI/2027-Materials/English/MI-H5926-8-0-AC-EN-27-S-508.pdf</t>
+  </si>
+  <si>
+    <t>2027 Annual Notice of Change – Molina Dual MI Coordinated Health (HMO D-SNP) - Barry, Branch, Calhoun, Kalamazoo, Van Buren</t>
+  </si>
+  <si>
+    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/MI/2027-Materials/English/MI-H5926-9-0-AC-EN-27-S-508.pdf</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>Summary of Benefits (SOB)</t>
+  </si>
+  <si>
+    <t>2027 Summary of Benefits - Molina Medicare Complete Care (HMO D-SNP)</t>
+  </si>
+  <si>
+    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/AZ/2027-Materials/English/AZ-H8845-1-0-SB-EN-27-S-508.pdf</t>
+  </si>
+  <si>
+    <t>TC002 AZ Plan Materials — Summary of Benefits (SOB)</t>
+  </si>
+  <si>
+    <t>Low Income Subsidy</t>
+  </si>
+  <si>
+    <t>2027 Low Income Subsidy - Molina Medicare Complete Care (HMO D-SNP)</t>
+  </si>
+  <si>
+    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/AZ/2027-Materials/English/AZ-H8845-1-0-LISCHART-EN-27-S-508.pdf</t>
+  </si>
+  <si>
+    <t>TC001 AZ Plan Materials — Low Income Subsidy</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>2027</t>
-  </si>
-  <si>
-    <t>Annual Notice of Change (ANOC)</t>
-  </si>
-  <si>
-    <t>2027 Annual Notice of Change – Molina Medicare Complete Care (HMO D-SNP)</t>
-  </si>
-  <si>
-    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/MI/2027-Materials/English/MI-H5926-1-0-AC-EN-27-S-508.pdf</t>
-  </si>
-  <si>
-    <t>2027 Annual Notice of Change – Molina Dual MI Coordinated Health (HMO D-SNP) - Macomb, Wayne</t>
-  </si>
-  <si>
-    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/MI/2027-Materials/English/MI-H5926-8-0-AC-EN-27-S-508.pdf</t>
-  </si>
-  <si>
-    <t>2027 Annual Notice of Change – Molina Dual MI Coordinated Health (HMO D-SNP) - Barry, Branch, Calhoun, Kalamazoo, Van Buren</t>
-  </si>
-  <si>
-    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/MI/2027-Materials/English/MI-H5926-9-0-AC-EN-27-S-508.pdf</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>Summary of Benefits (SOB)</t>
-  </si>
-  <si>
-    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/AZ/2027-Materials/English/AZ-H8845-1-0-SB-EN-27-S-508.pdf</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Low Income Subsidy</t>
-  </si>
-  <si>
-    <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/AZ/2027-Materials/English/AZ-H8845-1-0-LISCHART-EN-27-S-508.pdf</t>
-  </si>
-  <si>
-    <t>2027 Summary of Benefits - Molina Medicare Complete Care (HMO D-SNP)</t>
-  </si>
-  <si>
-    <t>2027 Low Income Subsidy - Molina Medicare Complete Care (HMO D-SNP)</t>
-  </si>
-  <si>
     <t>TX</t>
   </si>
   <si>
@@ -101,6 +113,9 @@
   </si>
   <si>
     <t>https://pws-q1.molinahealthcare.com/-/media/Project/PWS/Healthcare/PDF/Documents/Medicare/TX/2027-Materials/English/TX-H6515-1-0-AC-EN-27-S-508.pdf</t>
+  </si>
+  <si>
+    <t>TC004 TX Plan Materials — Annual Notice of Change (ANOC)</t>
   </si>
   <si>
     <t>2027 Annual Notice of Change – Molina Medicare Complete Care Plus (HMO D-SNP) - Dallas</t>
@@ -134,25 +149,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -175,23 +175,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -205,10 +198,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -533,274 +522,294 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.796875" customWidth="1"/>
-    <col min="2" max="3" width="6.796875" customWidth="1"/>
-    <col min="4" max="4" width="36.796875" customWidth="1"/>
-    <col min="5" max="5" width="82.796875" customWidth="1"/>
-    <col min="6" max="6" width="138.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="112.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2027</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2027</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2027</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2027</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2027</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2027</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2027</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3">
-        <v>2027</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2027</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3">
-        <v>2027</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2027</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2027</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>35</v>
+      <c r="G12" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{11DA54ED-875A-47FC-A535-9442085CA57B}"/>
-    <hyperlink ref="F8" r:id="rId2" xr:uid="{4F4BEFA9-5899-4D55-AB7D-A71148806C3B}"/>
-    <hyperlink ref="F9" r:id="rId3" xr:uid="{EF18621A-61A9-48DB-8F44-BD1FC320225E}"/>
-    <hyperlink ref="F10" r:id="rId4" xr:uid="{06ACE77F-7E21-48F1-976D-517FAC67CA35}"/>
-    <hyperlink ref="F11" r:id="rId5" xr:uid="{2F5F922E-10CE-437F-BE88-01DF3B02E539}"/>
-    <hyperlink ref="F12" r:id="rId6" xr:uid="{612FAA58-DCDB-4B01-ADEB-C084D5ECACC6}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 B3:F3 B2:D2 B4:E4 F2" numberStoredAsText="1"/>
+    <ignoredError sqref="C1:G12 A1:A12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" enabled="0" method="" siteId="{5e625f8d-0b53-4f56-9e46-19fa14bb2e5c}" removed="1"/>
-</clbl:labelList>
 </file>